--- a/task-reviews/diagrams/task_diagrams_hierarchy_ancestor_label/task_diagrams_hierarchy_ancestor_label.xlsx
+++ b/task-reviews/diagrams/task_diagrams_hierarchy_ancestor_label/task_diagrams_hierarchy_ancestor_label.xlsx
@@ -3029,7 +3029,199 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Wan and Pahl? Return the exact label shown. Respond with the exact label from the diagram.
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of As and Fry? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of As and Fry? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[213.0, 307.5, 377.0, 379.5]], "answer": "Susi"}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[213.0, 307.5, 377.0, 379.5]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>634757042505211</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0016.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="198.75" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Luis and Lael? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Luis and Lael? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[926.0, 530.0, 1090.0, 602.0]], "answer": "Cila"}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[926.0, 530.0, 1090.0, 602.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>656643176589949</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0000.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="198.75" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Frey and Uuge? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Frey and Uuge? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[190.0, 352.0, 354.0, 424.0]], "answer": "Gunn"}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[190.0, 352.0, 354.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1625945191797890</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0006.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="198.75" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Skye and Dyke? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
 Answer requirement: set "answer" to the exact visible ancestor label.
@@ -3037,63 +3229,127 @@
 {"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Wan and Pahl? Return the exact label shown. Respond with the exact label from the diagram.
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Skye and Dyke? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible ancestor label.
+Answer requirement: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[926.0, 530.0, 1090.0, 602.0]], "answer": "Jea"}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>[[926.0, 530.0, 1090.0, 602.0]]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[558.0, 441.0, 722.0, 513.0]], "answer": "Rech"}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[558.0, 441.0, 722.0, 513.0]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>119823626379211</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0002.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0002.json</t>
+      <c r="K5" t="n">
+        <v>2559815167116158</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0024.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0024.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="198.75" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="6" ht="198.75" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>lowest_common_ancestor_of_two_nodes</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Elum and Nett? Return the exact label shown. Give the full label exactly as shown.
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the lowest common ancestor of Mya and Radu? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the lowest common ancestor of Mya and Radu? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[190.0, 352.0, 354.0, 424.0]], "answer": "Tace"}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[190.0, 352.0, 354.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2950964841029597</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0022.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="198.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Neu and Gay? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
 Answer: set "answer" to the exact visible ancestor label.
@@ -3101,63 +3357,319 @@
 {"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Elum and Nett? Return the exact label shown. Give the full label exactly as shown.
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Neu and Gay? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[213.0, 307.5, 377.0, 379.5]], "answer": "Haas"}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[213.0, 307.5, 377.0, 379.5]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[926.0, 352.0, 1090.0, 424.0]], "answer": "Demp"}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[926.0, 352.0, 1090.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>130742008519036</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0018.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0018.json</t>
+      <c r="K7" t="n">
+        <v>3521540176379352</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0010.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0010.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="198.75" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="8" ht="198.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>lowest_common_ancestor_of_two_nodes</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Odo and Alys? Return the exact label shown. Answer using the exact visible label.
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Irra and Fink? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Irra and Fink? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[535.0, 174.0, 699.0, 246.0]], "answer": "Hoag"}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[535.0, 174.0, 699.0, 246.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>3538856232375832</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0013.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="198.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Ivey and Lula? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Ivey and Lula? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[558.0, 174.0, 722.0, 246.0]], "answer": "Baer"}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[558.0, 174.0, 722.0, 246.0]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>3710893278277015</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0012.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="198.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the lowest common ancestor of Born and Troy? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the lowest common ancestor of Born and Troy? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[282.0, 352.0, 446.0, 424.0]], "answer": "Chuu"}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[282.0, 352.0, 446.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>4142925151374938</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0017.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="198.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Guss and Gay? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Guss and Gay? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[190.0, 352.0, 354.0, 424.0]], "answer": "Yasu"}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[190.0, 352.0, 354.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>4763385411688484</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0007.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="198.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Oba and Heer? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
 Answer format: set "answer" to the exact visible ancestor label.
@@ -3165,63 +3677,63 @@
 {"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Odo and Alys? Return the exact label shown. Answer using the exact visible label.
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Oba and Heer? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible ancestor label.
+Answer requirement: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[282.0, 352.0, 446.0, 424.0]], "answer": "Drye"}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[282.0, 352.0, 446.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[634.667, 174.0, 798.667, 246.0]], "answer": "Nine"}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[634.667, 174.0, 798.667, 246.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>212076197186425</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0024.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0024.json</t>
+      <c r="K12" t="n">
+        <v>4856845598957412</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0011.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0011.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="198.75" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="13" ht="198.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>lowest_common_ancestor_of_two_nodes</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Sura and Acey? Return the exact label shown. Respond with the exact label from the diagram.
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Kemp and Gael? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
 Answer rule: set "answer" to the exact visible ancestor label.
@@ -3229,63 +3741,255 @@
 {"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Sura and Acey? Return the exact label shown. Respond with the exact label from the diagram.
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Kemp and Gael? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
+Answer requirement: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[788.0, 352.0, 952.0, 424.0]], "answer": "Eva"}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[926.0, 530.0, 1090.0, 602.0]], "answer": "Edra"}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[926.0, 530.0, 1090.0, 602.0]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4996674971013913</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0018.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="198.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Rodi and Algy? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Rodi and Algy? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[213.0, 307.5, 377.0, 379.5]], "answer": "Ier"}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[213.0, 307.5, 377.0, 379.5]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>5090339116762723</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0004.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="198.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Dene and Orin? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Dene and Orin? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[788.0, 352.0, 952.0, 424.0]], "answer": "Grof"}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>[[788.0, 352.0, 952.0, 424.0]]</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>291969049611262</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0008.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0008.json</t>
+      <c r="K15" t="n">
+        <v>5091536576120036</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0020.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0020.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="198.75" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="16" ht="198.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>lowest_common_ancestor_of_two_nodes</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Rip and Suu? Return the exact label shown. Return the exact visible label.
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Lat and Peer? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Lat and Peer? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[282.0, 352.0, 446.0, 424.0]], "answer": "Eben"}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[282.0, 352.0, 446.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>5149852164550107</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0002.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="198.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Lem and Lal? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
 Answer format: set "answer" to the exact visible ancestor label.
@@ -3293,63 +3997,319 @@
 {"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Rip and Suu? Return the exact label shown. Return the exact visible label.
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Lem and Lal? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[190.0, 441.0, 354.0, 513.0]], "answer": "Ihab"}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[190.0, 441.0, 354.0, 513.0]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[213.0, 307.5, 377.0, 379.5]], "answer": "Edny"}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[213.0, 307.5, 377.0, 379.5]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1195954398276634</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0017.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0017.json</t>
+      <c r="K17" t="n">
+        <v>5336604851483322</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0014.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0014.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="198.75" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="18" ht="198.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>lowest_common_ancestor_of_two_nodes</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Jit and Olli? Return the exact label shown. Return the exact visible label.
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Nine and Dett? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Nine and Dett? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[926.0, 352.0, 1090.0, 424.0]], "answer": "Dix"}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[926.0, 352.0, 1090.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5604554301717858</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0021.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="198.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Tav and Olds? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Tav and Olds? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[282.0, 352.0, 446.0, 424.0]], "answer": "Amie"}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[282.0, 352.0, 446.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5686951357492689</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0019.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="198.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Sara and Chu? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Sara and Chu? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[673.0, 574.5, 837.0, 646.5]], "answer": "Bran"}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[673.0, 574.5, 837.0, 646.5]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>6357490336064803</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0008.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="198.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Evyn and Asia? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Evyn and Asia? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[213.0, 307.5, 377.0, 379.5]], "answer": "Shae"}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[213.0, 307.5, 377.0, 379.5]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6381921547737134</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0005.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="198.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Khan and Nana? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
 Answer rule: set "answer" to the exact visible ancestor label.
@@ -3357,63 +4317,127 @@
 {"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Jit and Olli? Return the exact label shown. Return the exact visible label.
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Khan and Nana? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible ancestor label.
+Answer rule: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[535.0, 174.0, 699.0, 246.0]], "answer": "Bond"}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[535.0, 174.0, 699.0, 246.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[788.0, 352.0, 952.0, 424.0]], "answer": "Arde"}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[788.0, 352.0, 952.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1334156097139163</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0019.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0019.json</t>
+      <c r="K22" t="n">
+        <v>6647871526236408</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0001.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0001.json</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="198.75" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
+    <row r="23" ht="198.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>lowest_common_ancestor_of_two_nodes</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the lowest common ancestor of Phia and Bel? Return the exact label shown. Give the full label exactly as shown.
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Acie and Dalt? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Acie and Dalt? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[190.0, 352.0, 354.0, 424.0]], "answer": "Shem"}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[190.0, 352.0, 354.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>6853981572421553</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0023.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="198.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Till and Fae? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
 Answer field: set "answer" to the exact visible ancestor label.
@@ -3421,63 +4445,127 @@
 {"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the lowest common ancestor of Phia and Bel? Return the exact label shown. Give the full label exactly as shown.
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Till and Fae? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
+Answer rule: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[926.0, 441.0, 1090.0, 513.0]], "answer": "Giza"}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[558.0, 530.0, 722.0, 602.0]], "answer": "Bahr"}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[558.0, 530.0, 722.0, 602.0]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>7467687722691325</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0015.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="198.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>lowest_common_ancestor_of_two_nodes</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Oby and Buck? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Oby and Buck? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Cott"}</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[926.0, 441.0, 1090.0, 513.0]], "answer": "Flo"}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>[[926.0, 441.0, 1090.0, 513.0]]</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>2219470342823660</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0015.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0015.json</t>
+      <c r="K25" t="n">
+        <v>7754554261398830</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0003.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0003.json</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="198.75" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
+    <row r="26" ht="198.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>lowest_common_ancestor_of_two_nodes</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Dalt and Lose? Return the exact label shown. Respond with the exact label from the diagram.
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Fi and Seto? Return the exact label shown. Give the full label exactly as shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
 Answer requirement: set "answer" to the exact visible ancestor label.
@@ -3485,1134 +4573,46 @@
 {"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Dalt and Lose? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[788.0, 352.0, 952.0, 424.0]], "answer": "Edda"}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[788.0, 352.0, 952.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2263110604332923</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0023.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="198.75" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Joon and Blau? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer rule: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Joon and Blau? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[634.667, 174.0, 798.667, 246.0]], "answer": "Tien"}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[634.667, 174.0, 798.667, 246.0]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2460879606342527</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0014.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="198.75" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Joon and Fi? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer rule: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Joon and Fi? Return the exact label shown. Respond with the exact label from the diagram.
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Fi and Seto? Return the exact label shown. Give the full label exactly as shown.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Cott"}</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[282.0, 352.0, 446.0, 424.0]], "answer": "Dana"}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[282.0, 352.0, 446.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[673.0, 574.5, 837.0, 646.5]], "answer": "Etom"}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[673.0, 574.5, 837.0, 646.5]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>2633281752199345</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0016.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="198.75" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Dosh and Shih? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Dosh and Shih? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[673.0, 574.5, 837.0, 646.5]], "answer": "Dong"}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[673.0, 574.5, 837.0, 646.5]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3348992816087131</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K26" t="n">
+        <v>8384374793269193</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0009.png</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="198.75" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Jala and Lusa? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer rule: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Jala and Lusa? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[926.0, 530.0, 1090.0, 602.0]], "answer": "Jade"}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[926.0, 530.0, 1090.0, 602.0]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>3699131626340868</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0012.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="198.75" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Dene and Cupo? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Dene and Cupo? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[282.0, 352.0, 446.0, 424.0]], "answer": "Cade"}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[282.0, 352.0, 446.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>3869926740309152</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0006.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0006.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="198.75" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Roda and Musa? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Roda and Musa? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[282.0, 352.0, 446.0, 424.0]], "answer": "Gula"}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[282.0, 352.0, 446.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>4031464386473246</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0000.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="198.75" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Baxy and Tacy? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Baxy and Tacy? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[213.0, 307.5, 377.0, 379.5]], "answer": "Arin"}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[213.0, 307.5, 377.0, 379.5]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>4914632647641257</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0001.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0001.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="198.75" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Body and Kyl? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the lowest common ancestor of Body and Kyl? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[282.0, 352.0, 446.0, 424.0]], "answer": "Yoko"}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[282.0, 352.0, 446.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>5156314087922847</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0007.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="198.75" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Oza and Huda? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the lowest common ancestor of Oza and Huda? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[558.0, 174.0, 722.0, 246.0]], "answer": "Aryn"}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[558.0, 174.0, 722.0, 246.0]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>5844346174875529</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0003.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="198.75" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the lowest common ancestor of Jann and Emie? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the lowest common ancestor of Jann and Emie? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[634.667, 174.0, 798.667, 246.0]], "answer": "Kip"}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[634.667, 174.0, 798.667, 246.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>6563450745719465</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0005.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="198.75" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Tess and Lesh? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Tess and Lesh? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[634.667, 174.0, 798.667, 246.0]], "answer": "Bick"}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[634.667, 174.0, 798.667, 246.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>6592996695784009</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0010.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="198.75" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Ilse and Om? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Ilse and Om? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[190.0, 441.0, 354.0, 513.0]], "answer": "Lars"}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[190.0, 441.0, 354.0, 513.0]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>6768702801708091</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0011.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="198.75" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Blim and Caro? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Blim and Caro? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[673.0, 574.5, 837.0, 646.5]], "answer": "Kehr"}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[673.0, 574.5, 837.0, 646.5]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>7347179606883608</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0020.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="198.75" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Berk and Atul? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the lowest common ancestor of Berk and Atul? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[190.0, 352.0, 354.0, 424.0]], "answer": "Lea"}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[190.0, 352.0, 354.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>7651181528767617</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0004.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="198.75" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Yves and Fair? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer rule: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Yves and Fair? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[673.0, 574.5, 837.0, 646.5]], "answer": "Nam"}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[673.0, 574.5, 837.0, 646.5]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>7981418648354305</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0021.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="198.75" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the lowest common ancestor of Nady and Bing? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the lowest common ancestor of Nady and Bing? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[926.0, 441.0, 1090.0, 513.0]], "answer": "Ches"}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[926.0, 441.0, 1090.0, 513.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8073448277617879</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0013.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="198.75" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>lowest_common_ancestor_of_two_nodes</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Gary and Buna? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct ancestor box.
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[558,530,722,602]],"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the lowest common ancestor of Gary and Buna? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Cott"}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[558.0, 174.0, 722.0, 246.0]], "answer": "Myra"}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[558.0, 174.0, 722.0, 246.0]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>8583933955199259</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/lowest_common_ancestor_of_two_nodes/0022.png</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/lowest_common_ancestor_of_two_nodes/0022.json</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,391 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Diao? Return the exact label shown. Answer with the exact label shown.
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Ken? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Ken? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[558.0, 530.0, 722.0, 602.0]], "answer": "Le"}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[558.0, 530.0, 722.0, 602.0]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>387946866803488</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0018.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="198.75" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Diba? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Diba? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[190.0, 352.0, 354.0, 424.0]], "answer": "Ara"}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[190.0, 352.0, 354.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>394763918625841</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0019.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="198.75" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Cori? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Cori? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[926.0, 441.0, 1090.0, 513.0]], "answer": "Pry"}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[926.0, 441.0, 1090.0, 513.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>603662464569091</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0023.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="198.75" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Taub? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Taub? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[558.0, 530.0, 722.0, 602.0]], "answer": "Mir"}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[558.0, 530.0, 722.0, 602.0]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>879306409050044</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0024.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="198.75" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Illa? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Illa? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[558.0, 530.0, 722.0, 602.0]], "answer": "Arte"}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[558.0, 530.0, 722.0, 602.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1322802460237092</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0014.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="198.75" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Ira? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Ira? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[558.0, 530.0, 722.0, 602.0]], "answer": "Jaye"}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[558.0, 530.0, 722.0, 602.0]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1622241020596727</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0022.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="198.75" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Isla? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
 Answer requirement: set "answer" to the exact visible ancestor label.
@@ -4734,63 +5118,191 @@
 {"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Diao? Return the exact label shown. Answer with the exact label shown.
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Isla? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[673.0, 307.5, 837.0, 379.5]], "answer": "Kunz"}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[673.0, 307.5, 837.0, 379.5]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1772649578574161</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0015.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="198.75" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Rivy? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Rivy? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[673.0, 307.5, 837.0, 379.5]], "answer": "Les"}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>[[673.0, 307.5, 837.0, 379.5]]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[190.0, 441.0, 354.0, 513.0]], "answer": "Temp"}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[190.0, 441.0, 354.0, 513.0]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>189952578223858</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0024.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0024.json</t>
+      <c r="K9" t="n">
+        <v>2125425567326588</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0007.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0007.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="198.75" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="10" ht="198.75" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>parent_of_node</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Sib? Return the exact label shown. Answer with the exact label shown.
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Can? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Can? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[788.0, 352.0, 952.0, 424.0]], "answer": "Mun"}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[788.0, 352.0, 952.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2154741142237988</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0017.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="198.75" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Lura? Return the exact label shown. Respond with the exact label from the diagram.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
 Answer requirement: set "answer" to the exact visible ancestor label.
@@ -4798,63 +5310,383 @@
 {"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Sib? Return the exact label shown. Answer with the exact label shown.
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Lura? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[926.0, 352.0, 1090.0, 424.0]], "answer": "Edda"}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[926.0, 352.0, 1090.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2181407946772823</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0001.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="198.75" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Swan? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Swan? Return the exact label shown. Respond with the exact label from the diagram.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[926.0, 530.0, 1090.0, 602.0]], "answer": "Bord"}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[926.0, 530.0, 1090.0, 602.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2741590803703885</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0002.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="198.75" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Toby? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Toby? Return the exact label shown. Give the full label exactly as shown.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[190.0, 441.0, 354.0, 513.0]], "answer": "Ursi"}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[190.0, 441.0, 354.0, 513.0]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[558.0, 530.0, 722.0, 602.0]], "answer": "Iva"}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[558.0, 530.0, 722.0, 602.0]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>850855665898786</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0005.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0005.json</t>
+      <c r="K13" t="n">
+        <v>2934783767347701</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0020.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0020.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="198.75" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="14" ht="198.75" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>parent_of_node</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Jac? Return the exact label shown. Answer using the exact visible label.
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Wini? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Wini? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[558.0, 530.0, 722.0, 602.0]], "answer": "Cran"}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[558.0, 530.0, 722.0, 602.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3500016541635510</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0021.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="198.75" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Olds? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Olds? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[558.0, 530.0, 722.0, 602.0]], "answer": "Dann"}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[558.0, 530.0, 722.0, 602.0]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3734692986597999</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0000.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="198.75" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Bowe? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Bowe? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[673.0, 574.5, 837.0, 646.5]], "answer": "Keir"}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[673.0, 574.5, 837.0, 646.5]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4505555467065461</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0011.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="198.75" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Lat? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
 Answer: set "answer" to the exact visible ancestor label.
@@ -4862,319 +5694,127 @@
 {"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Jac? Return the exact label shown. Answer using the exact visible label.
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Lat? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
+Answer field: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[926.0, 530.0, 1090.0, 602.0]], "answer": "Oz"}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[926.0, 530.0, 1090.0, 602.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[926.0, 352.0, 1090.0, 424.0]], "answer": "Mich"}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[926.0, 352.0, 1090.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>860449350006202</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0009.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0009.json</t>
+      <c r="K17" t="n">
+        <v>4594042114155407</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0016.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0016.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="198.75" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="18" ht="198.75" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>parent_of_node</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Len? Return the exact label shown. Answer using the exact visible label.
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Roy? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer: set "answer" to the exact visible ancestor label.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer field: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Len? Return the exact label shown. Answer using the exact visible label.
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Roy? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible ancestor label.
+Answer rule: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[926.0, 352.0, 1090.0, 424.0]], "answer": "Ming"}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[926.0, 352.0, 1090.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[788.0, 352.0, 952.0, 424.0]], "answer": "Nara"}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[788.0, 352.0, 952.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1817954464213404</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0000.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0000.json</t>
+      <c r="K18" t="n">
+        <v>5343099063995316</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0008.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0008.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="198.75" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="19" ht="198.75" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>parent_of_node</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Peta? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Peta? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[788.0, 352.0, 952.0, 424.0]], "answer": "Virg"}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[788.0, 352.0, 952.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1836106835844707</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0008.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="198.75" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Pia? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Pia? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[282.0, 352.0, 446.0, 424.0]], "answer": "Nath"}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[282.0, 352.0, 446.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1860420609506854</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0013.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="198.75" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Lamb? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Lamb? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[673.0, 441.0, 837.0, 513.0]], "answer": "Ban"}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[673.0, 441.0, 837.0, 513.0]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2008102795882840</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0003.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="198.75" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Audi? Return the exact label shown. Answer with the exact label shown.
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Pier? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
 Answer format: set "answer" to the exact visible ancestor label.
@@ -5182,63 +5822,127 @@
 {"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Audi? Return the exact label shown. Answer with the exact label shown.
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Pier? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible ancestor label.
+Answer requirement: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[558.0, 530.0, 722.0, 602.0]], "answer": "Cos"}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[558.0, 530.0, 722.0, 602.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[213.0, 307.5, 377.0, 379.5]], "answer": "Ben"}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[213.0, 307.5, 377.0, 379.5]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>2919859047062069</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0010.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0010.json</t>
+      <c r="K19" t="n">
+        <v>5649428683534583</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0004.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0004.json</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="198.75" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
+    <row r="20" ht="198.75" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>parent_of_node</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Bust? Return the exact label shown. Give the full label exactly as shown.
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Rabi? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Rabi? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[926.0, 441.0, 1090.0, 513.0]], "answer": "Bass"}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[926.0, 441.0, 1090.0, 513.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5762683078527150</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0012.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="198.75" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Bigg? Return the exact label shown. Answer with the exact label shown.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
 Answer format: set "answer" to the exact visible ancestor label.
@@ -5246,127 +5950,255 @@
 {"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Bust? Return the exact label shown. Give the full label exactly as shown.
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Bigg? Return the exact label shown. Answer with the exact label shown.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[190.0, 352.0, 354.0, 424.0]], "answer": "Rees"}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[190.0, 352.0, 354.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6153442497440690</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0010.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="198.75" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Veno? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Veno? Return the exact label shown. Give the full label exactly as shown.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[788.0, 352.0, 952.0, 424.0]], "answer": "Dahl"}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[788.0, 352.0, 952.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>6216325838607184</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0013.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="198.75" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Myna? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer rule: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Myna? Return the exact label shown. Answer using the exact visible label.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[673.0, 574.5, 837.0, 646.5]], "answer": "Bass"}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[673.0, 574.5, 837.0, 646.5]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>6240274830812744</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0003.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="198.75" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_diagrams_hierarchy_ancestor_label</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>parent_of_node</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Clim? Return the exact label shown. Return the exact visible label.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
+Answer format: set "answer" to the exact visible ancestor label.
+Example JSON:
+{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Clim? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[926.0, 530.0, 1090.0, 602.0]], "answer": "Yuri"}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[926.0, 530.0, 1090.0, 602.0]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[673.0, 574.5, 837.0, 646.5]], "answer": "Wane"}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[673.0, 574.5, 837.0, 646.5]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>3502714669160731</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0002.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0002.json</t>
+      <c r="K24" t="n">
+        <v>6258645524788493</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0005.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0005.json</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="198.75" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
+    <row r="25" ht="198.75" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>parent_of_node</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Elke? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Elke? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[926.0, 352.0, 1090.0, 424.0]], "answer": "Diaz"}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[926.0, 352.0, 1090.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>4065652413170682</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0017.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="198.75" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Wall? Return the exact label shown. Return the exact visible label.
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Samy? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
 Answer field: set "answer" to the exact visible ancestor label.
@@ -5374,319 +6206,63 @@
 {"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Wall? Return the exact label shown. Return the exact visible label.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Samy? Return the exact label shown. Answer using the exact visible label.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible ancestor label.
+Answer format: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[190.0, 441.0, 354.0, 513.0]], "answer": "Livi"}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[190.0, 441.0, 354.0, 513.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[926.0, 352.0, 1090.0, 424.0]], "answer": "Edme"}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[926.0, 352.0, 1090.0, 424.0]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>4153455206039775</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K25" t="n">
+        <v>6303102455678309</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0006.png</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0006.json</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="198.75" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
+    <row r="26" ht="198.75" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_diagrams_hierarchy_ancestor_label</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>parent_of_node</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Dyna? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Dyna? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[558.0, 530.0, 722.0, 602.0]], "answer": "Ax"}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[558.0, 530.0, 722.0, 602.0]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>4758734107737553</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0019.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="198.75" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Mert? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Mert? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[926.0, 352.0, 1090.0, 424.0]], "answer": "Cad"}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[926.0, 352.0, 1090.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>4942762588420821</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0004.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="198.75" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Bari? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Bari? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[190.0, 352.0, 354.0, 424.0]], "answer": "Clay"}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[190.0, 352.0, 354.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>5301162925494134</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0020.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="198.75" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Byrn? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Byrn? Return the exact label shown. Answer using the exact visible label.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[788.0, 352.0, 952.0, 424.0]], "answer": "Kela"}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[788.0, 352.0, 952.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>5301258275454684</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0021.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="198.75" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Nel? Return the exact label shown. Give the full label exactly as shown.
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Sax? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
 Answer rule: set "answer" to the exact visible ancestor label.
@@ -5694,622 +6270,46 @@
 {"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Nel? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[558.0, 352.0, 722.0, 424.0]], "answer": "Klos"}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[558.0, 352.0, 722.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>5402567681741744</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0011.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="198.75" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Law? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Work from the labeled parent-child structure: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Law? Return the exact label shown. Return the exact visible label.
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Sax? Return the exact label shown. Return the exact visible label.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the exact visible ancestor label.
 Example JSON:
 {"answer":"Walt"}</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[558.0, 441.0, 722.0, 513.0]], "answer": "Ruy"}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[558.0, 441.0, 722.0, 513.0]], "answer": "Bea"}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>[[558.0, 441.0, 722.0, 513.0]]</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>6818872353916774</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0012.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="198.75" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Dorr? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer rule: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. What is the parent of Dorr? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[190.0, 441.0, 354.0, 513.0]], "answer": "Tray"}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[190.0, 441.0, 354.0, 513.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>6837806743300142</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0023.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="198.75" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Lil? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Lil? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[926.0, 530.0, 1090.0, 602.0]], "answer": "Rapp"}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[926.0, 530.0, 1090.0, 602.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>6873593084663462</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0022.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="198.75" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Aria? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Aria? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[535.0, 174.0, 699.0, 246.0]], "answer": "Lati"}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[535.0, 174.0, 699.0, 246.0]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>7399228533812148</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0007.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="198.75" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Ole? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Determine the requested ancestor from the hierarchy: What is the parent of Ole? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[1018.0, 307.5, 1182.0, 379.5]], "answer": "Mar"}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[1018.0, 307.5, 1182.0, 379.5]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>8114727966633317</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0001.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0001.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="198.75" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Olfe? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Look at the hierarchy diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Olfe? Return the exact label shown. Give the full label exactly as shown.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[558.0, 174.0, 722.0, 246.0]], "answer": "Vola"}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[558.0, 174.0, 722.0, 246.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>8604620266612327</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0014.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="198.75" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Ame? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer format: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a hierarchical org chart with labeled boxes and parent-child connector lines. Use the hierarchy to answer: What is the parent of Ame? Return the exact label shown. Return the exact visible label.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[926.0, 530.0, 1090.0, 602.0]], "answer": "Tina"}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[926.0, 530.0, 1090.0, 602.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>8684254629469135</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0015.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="198.75" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Huba? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer requirement: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Use the hierarchical diagram in the image: a hierarchical org chart with labeled boxes and parent-child connector lines. Read the labeled org chart and answer: What is the parent of Huba? Return the exact label shown. Respond with the exact label from the diagram.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[634.667, 174.0, 798.667, 246.0]], "answer": "Al"}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[634.667, 174.0, 798.667, 246.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8917631406617910</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0016.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="198.75" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_diagrams_hierarchy_ancestor_label</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>parent_of_node</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Pate? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the correct parent box.
-Answer field: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"evidence":[[926,352,1090,424]],"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>You are given a hierarchical org chart with labeled boxes and parent-child connector lines. Follow the parent-child structure and answer: What is the parent of Pate? Return the exact label shown. Answer with the exact label shown.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact visible ancestor label.
-Example JSON:
-{"answer":"Walt"}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[190.0, 352.0, 354.0, 424.0]], "answer": "Rube"}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[190.0, 352.0, 354.0, 424.0]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>8961090759141545</v>
+        <v>6673221308763839</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0018.png</t>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/images/parent_of_node/0009.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0018.json</t>
+          <t>diagrams/task_diagrams_hierarchy_ancestor_label/data/parent_of_node/0009.json</t>
         </is>
       </c>
     </row>
